--- a/TP2026/Exercices_TP8.xlsx
+++ b/TP2026/Exercices_TP8.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{587FBA61-F06E-4E94-9E23-22DBE4F804BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E11E3D-4308-4CEE-B733-609565694312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77D2F8F8-3EAB-4FD5-8A99-8A7B70AECDED}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="129">
   <si>
     <t>Montant (DH) = Prix unitaire (DH) * Quantité</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Légumes</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>Fruits</t>
   </si>
   <si>
@@ -248,13 +245,7 @@
     <t>Match 3</t>
   </si>
   <si>
-    <t>Meilleure perf.</t>
-  </si>
-  <si>
     <t>Match 4</t>
-  </si>
-  <si>
-    <t>Plus mauvaise perf.</t>
   </si>
   <si>
     <t>Match 5</t>
@@ -428,6 +419,18 @@
   </si>
   <si>
     <t>Économie = Prix initial * Réduction % /100</t>
+  </si>
+  <si>
+    <t>Victoire = 3 points ; Nul = 1 point ; Défaite = 0 point</t>
+  </si>
+  <si>
+    <t>Meilleure performance</t>
+  </si>
+  <si>
+    <t>Plus mauvaise performance</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -981,6 +984,126 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1009,68 +1132,8 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1083,66 +1146,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -1166,16 +1169,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>118110</xdr:rowOff>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>235373</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>555413</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1198,7 +1201,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6202680" y="4171950"/>
+          <a:off x="5753100" y="4232910"/>
           <a:ext cx="4906433" cy="1162050"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1210,16 +1213,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>403860</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>49014</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>739140</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>26154</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1243,7 +1246,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8503920" y="8016240"/>
+          <a:off x="6416040" y="8176260"/>
           <a:ext cx="1798320" cy="1024374"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1255,16 +1258,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>7621</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>304801</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>76201</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>327661</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>6723</xdr:rowOff>
+      <xdr:rowOff>67683</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1287,7 +1290,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7383781" y="10477500"/>
+          <a:off x="6316981" y="10538460"/>
           <a:ext cx="4983480" cy="1172583"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1299,23 +1302,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>106735</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>673544</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>62621</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>77493</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Image 5">
+        <xdr:cNvPr id="8" name="Image 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50D8E8D6-52DF-4BB2-A0A0-AB8B83395AA1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07214DF2-6685-4A48-B09F-CE2515E1F80B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1331,8 +1334,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7376160" y="12573055"/>
-          <a:ext cx="4803584" cy="1418926"/>
+          <a:off x="5227320" y="1783080"/>
+          <a:ext cx="3788433" cy="1577340"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1344,22 +1347,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>7621</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>160020</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>862353</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>107061</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Image 7">
+        <xdr:cNvPr id="3" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07214DF2-6685-4A48-B09F-CE2515E1F80B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA74325-4979-5A29-873E-1B9957A8EA61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1375,8 +1378,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5913120" y="1767840"/>
-          <a:ext cx="3788433" cy="1577340"/>
+          <a:off x="6019801" y="6134100"/>
+          <a:ext cx="5060060" cy="1158240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1387,23 +1390,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>76</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>117944</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>487680</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>131655</xdr:rowOff>
+      <xdr:colOff>498318</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Image 10">
+        <xdr:cNvPr id="7" name="Image 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B92F1EE-F8D5-16F3-5F54-771B240FB310}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D70075F9-FAA0-3D58-4CD8-EBB49B878608}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1419,8 +1422,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6995160" y="14859000"/>
-          <a:ext cx="4465320" cy="1305135"/>
+          <a:off x="6614160" y="12401384"/>
+          <a:ext cx="5542758" cy="1596556"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1432,22 +1435,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>548641</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>15621</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>662940</xdr:colOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>106538</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Image 2">
+        <xdr:cNvPr id="9" name="Image 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EBA74325-4979-5A29-873E-1B9957A8EA61}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C6A77BA-504B-DD94-EA84-3247B7E4B178}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1463,8 +1466,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6560821" y="6217920"/>
-          <a:ext cx="5060060" cy="1158240"/>
+          <a:off x="6499860" y="14874240"/>
+          <a:ext cx="4511040" cy="1264778"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1801,8 +1804,9 @@
   <cols>
     <col min="1" max="1" width="3" style="2" customWidth="1"/>
     <col min="2" max="2" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15" style="2" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.6640625" style="2"/>
     <col min="8" max="8" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
@@ -1821,7 +1825,7 @@
   <sheetData>
     <row r="2" spans="2:31" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -1829,32 +1833,32 @@
     </row>
     <row r="4" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+        <v>89</v>
+      </c>
+      <c r="C4" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
       <c r="G4" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="H4" s="5">
         <f ca="1">TODAY()</f>
-        <v>46061</v>
+        <v>46062</v>
       </c>
     </row>
     <row r="5" spans="2:31" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="C5" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="66" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="66"/>
+      <c r="E5" s="66"/>
+      <c r="G5" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="G5" s="4" t="s">
-        <v>96</v>
       </c>
       <c r="H5" s="7">
         <f>D135</f>
@@ -1862,24 +1866,24 @@
       </c>
     </row>
     <row r="7" spans="2:31" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="33" t="s">
+      <c r="B7" s="63" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
+      <c r="F7" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="64"/>
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.3">
       <c r="AE8" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.3">
@@ -1896,7 +1900,7 @@
         <v>4</v>
       </c>
       <c r="AE9" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:31" x14ac:dyDescent="0.3">
@@ -1910,15 +1914,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE10" s="9" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B11" s="14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="15">
         <v>12</v>
@@ -1927,15 +1931,15 @@
         <v>12</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE11" s="9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B12" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="12">
         <v>8</v>
@@ -1944,15 +1948,15 @@
         <v>65</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE12" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B13" s="14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="15">
         <v>4</v>
@@ -1961,15 +1965,15 @@
         <v>45</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE13" s="9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B14" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" s="12">
         <v>30</v>
@@ -1978,15 +1982,15 @@
         <v>2</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE14" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B15" s="14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="15">
         <v>20</v>
@@ -1995,15 +1999,15 @@
         <v>6</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE15" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.3">
       <c r="B16" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="12">
         <v>10</v>
@@ -2012,58 +2016,58 @@
         <v>15</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="AE16" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="36" t="s">
+      <c r="B17" s="67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="63"/>
+      <c r="D20" s="63"/>
+      <c r="E20" s="63"/>
+      <c r="F20" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="17" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="2:17" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="32" t="s">
-        <v>124</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="64"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="D22" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="F22" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B23" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="12">
         <v>14</v>
@@ -2075,12 +2079,12 @@
         <v>15</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B24" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="15">
         <v>12</v>
@@ -2092,12 +2096,12 @@
         <v>14</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B25" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="12">
         <v>15</v>
@@ -2109,12 +2113,12 @@
         <v>16</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B26" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C26" s="15">
         <v>10</v>
@@ -2126,12 +2130,12 @@
         <v>11</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B27" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C27" s="12">
         <v>16</v>
@@ -2143,53 +2147,53 @@
         <v>17</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="2:17" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="34"/>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="34"/>
+      <c r="B30" s="63" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
+      <c r="F30" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="G30" s="64"/>
+      <c r="H30" s="64"/>
+      <c r="I30" s="64"/>
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="65"/>
+      <c r="N30" s="65"/>
+      <c r="O30" s="65"/>
+      <c r="P30" s="65"/>
+      <c r="Q30" s="65"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="D32" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="E32" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="F32" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="12">
         <v>150</v>
@@ -2198,15 +2202,15 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="15">
         <v>400</v>
@@ -2215,15 +2219,15 @@
         <v>25</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="12">
         <v>600</v>
@@ -2232,15 +2236,15 @@
         <v>30</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="15">
         <v>800</v>
@@ -2249,28 +2253,28 @@
         <v>15</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
+      <c r="B37" s="68" t="s">
+        <v>115</v>
+      </c>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
       <c r="E37" s="18" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="40" spans="2:6" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="19" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C40" s="19"/>
       <c r="D40" s="19"/>
@@ -2278,77 +2282,77 @@
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="E42" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="F42" s="10" t="s">
         <v>37</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43" s="12">
         <v>900</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="15">
         <v>1000</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="12">
         <v>1000</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="15">
         <v>2000</v>
       </c>
       <c r="E46" s="21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="12">
         <v>1600</v>
@@ -2356,56 +2360,64 @@
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C48" s="15">
         <v>2800</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49" s="12">
         <v>1900</v>
       </c>
     </row>
-    <row r="52" spans="2:6" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B53" s="42" t="s">
+    <row r="52" spans="2:11" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="63" t="s">
+        <v>107</v>
+      </c>
+      <c r="C52" s="63"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
+      <c r="F52" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G52" s="64"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="64"/>
+      <c r="J52" s="64"/>
+      <c r="K52" s="64"/>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B53" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="62"/>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B55" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B55" s="23" t="s">
+      <c r="C55" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="D55" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="D55" s="23" t="s">
+      <c r="E55" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E55" s="23" t="s">
+      <c r="F55" s="23" t="s">
         <v>54</v>
       </c>
-      <c r="F55" s="23" t="s">
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B56" s="12" t="s">
         <v>55</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B56" s="12" t="s">
-        <v>56</v>
       </c>
       <c r="C56" s="12">
         <v>18</v>
@@ -2417,12 +2429,12 @@
         <v>3</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C57" s="15">
         <v>20</v>
@@ -2434,12 +2446,12 @@
         <v>2</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="12">
         <v>15</v>
@@ -2451,12 +2463,12 @@
         <v>3</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C59" s="15">
         <v>12</v>
@@ -2468,12 +2480,12 @@
         <v>8</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.3">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="12">
         <v>10</v>
@@ -2485,112 +2497,112 @@
         <v>9</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="32" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B64" s="62" t="s">
         <v>61</v>
       </c>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B64" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="42"/>
-      <c r="D64" s="42"/>
-      <c r="E64" s="42"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="62"/>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B66" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="C66" s="23" t="s">
-        <v>64</v>
-      </c>
       <c r="E66" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66" s="23" t="s">
         <v>37</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B67" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C67" s="12">
         <v>2</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F67" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B68" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C68" s="15">
         <v>0</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F68" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B69" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C69" s="12">
         <v>3</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="F69" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B70" s="14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="F70" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B71" s="11" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C71" s="12">
         <v>2</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F71" s="22" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B72" s="14" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C72" s="15">
         <v>4</v>
@@ -2598,45 +2610,45 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B73" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C73" s="12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:6" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="32" t="s">
-        <v>111</v>
-      </c>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
+      <c r="B75" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="C75" s="63"/>
+      <c r="D75" s="63"/>
+      <c r="E75" s="63"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B76" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="42"/>
-      <c r="D76" s="42"/>
-      <c r="E76" s="42"/>
+      <c r="B76" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C76" s="62"/>
+      <c r="D76" s="62"/>
+      <c r="E76" s="62"/>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B78" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E78" s="24" t="s">
         <v>78</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" s="24" t="s">
-        <v>80</v>
-      </c>
-      <c r="E78" s="24" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B79" s="25" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C79" s="25">
         <v>20</v>
@@ -2645,12 +2657,12 @@
         <v>120</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B80" s="27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C80" s="27">
         <v>25</v>
@@ -2659,12 +2671,12 @@
         <v>140</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="81" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B81" s="25" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C81" s="25">
         <v>30</v>
@@ -2673,12 +2685,12 @@
         <v>165</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="82" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B82" s="27" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C82" s="27">
         <v>35</v>
@@ -2687,12 +2699,12 @@
         <v>180</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B83" s="25" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C83" s="25">
         <v>40</v>
@@ -2701,67 +2713,67 @@
         <v>200</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="84" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B84" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C84" s="40"/>
-      <c r="D84" s="41"/>
+      <c r="B84" s="59" t="s">
+        <v>84</v>
+      </c>
+      <c r="C84" s="60"/>
+      <c r="D84" s="61"/>
       <c r="E84" s="28" t="s">
-        <v>6</v>
+        <v>128</v>
       </c>
     </row>
     <row r="86" spans="2:7" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C86" s="43"/>
-      <c r="D86" s="43"/>
-      <c r="E86" s="43"/>
+      <c r="B86" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
     </row>
     <row r="87" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="88" spans="2:7" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C88" s="44"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="F88" s="46"/>
-      <c r="G88" s="47"/>
+      <c r="B88" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C88" s="46"/>
+      <c r="D88" s="46"/>
+      <c r="E88" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="F88" s="48"/>
+      <c r="G88" s="49"/>
     </row>
     <row r="89" spans="2:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="44"/>
-      <c r="C89" s="44"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="48"/>
-      <c r="F89" s="49"/>
-      <c r="G89" s="50"/>
+      <c r="B89" s="46"/>
+      <c r="C89" s="46"/>
+      <c r="D89" s="46"/>
+      <c r="E89" s="50"/>
+      <c r="F89" s="51"/>
+      <c r="G89" s="52"/>
     </row>
     <row r="90" spans="2:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="48"/>
-      <c r="F90" s="49"/>
-      <c r="G90" s="50"/>
+      <c r="B90" s="46"/>
+      <c r="C90" s="46"/>
+      <c r="D90" s="46"/>
+      <c r="E90" s="50"/>
+      <c r="F90" s="51"/>
+      <c r="G90" s="52"/>
     </row>
     <row r="91" spans="2:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="44"/>
-      <c r="C91" s="44"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="53"/>
+      <c r="B91" s="46"/>
+      <c r="C91" s="46"/>
+      <c r="D91" s="46"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="55"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="30" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="95" spans="2:7" x14ac:dyDescent="0.3">
@@ -2860,414 +2872,409 @@
       <c r="F108"/>
     </row>
     <row r="109" spans="2:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="B109" s="54"/>
-      <c r="C109" s="55" t="str">
+      <c r="B109" s="32"/>
+      <c r="C109" s="33" t="str">
         <f>B4</f>
         <v>Nom et Prénom :</v>
       </c>
-      <c r="D109" s="55" t="str">
+      <c r="D109" s="33" t="str">
         <f>C4</f>
         <v>_______________________________</v>
       </c>
-      <c r="E109" s="55"/>
-      <c r="F109" s="55"/>
+      <c r="E109" s="33"/>
+      <c r="F109" s="33"/>
     </row>
     <row r="110" spans="2:7" ht="18" x14ac:dyDescent="0.35">
-      <c r="B110" s="54"/>
-      <c r="C110" s="55" t="str">
+      <c r="B110" s="32"/>
+      <c r="C110" s="33" t="str">
         <f>B5</f>
         <v>Classe :</v>
       </c>
-      <c r="D110" s="55" t="str">
+      <c r="D110" s="33" t="str">
         <f>C5</f>
         <v>_______________________________</v>
       </c>
-      <c r="E110" s="55"/>
-      <c r="F110" s="55"/>
+      <c r="E110" s="33"/>
+      <c r="F110" s="33"/>
     </row>
     <row r="111" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B111" s="54"/>
-      <c r="C111" s="54"/>
-      <c r="D111" s="54"/>
-      <c r="E111" s="54"/>
-      <c r="F111" s="54"/>
+      <c r="B111" s="32"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="32"/>
+      <c r="E111" s="32"/>
+      <c r="F111" s="32"/>
     </row>
     <row r="112" spans="2:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="54"/>
-      <c r="C112" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D112" s="57"/>
-      <c r="E112" s="58"/>
-      <c r="F112" s="54"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="D112" s="72"/>
+      <c r="E112" s="73"/>
+      <c r="F112" s="32"/>
     </row>
     <row r="113" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B113" s="54"/>
-      <c r="C113" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="D113" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="E113" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="F113" s="54"/>
+      <c r="B113" s="32"/>
+      <c r="C113" s="34" t="s">
+        <v>110</v>
+      </c>
+      <c r="D113" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="E113" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F113" s="32"/>
     </row>
     <row r="114" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="61" t="s">
-        <v>114</v>
-      </c>
-      <c r="C114" s="62" t="str">
+      <c r="B114" s="45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C114" s="37" t="str">
         <f>E9</f>
         <v>Total</v>
       </c>
-      <c r="D114" s="62">
+      <c r="D114" s="37">
         <f>IF(AND(_xlfn.ISFORMULA(E10),E10=C10*D10),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E114" s="63">
+      <c r="E114" s="38">
         <v>1</v>
       </c>
-      <c r="F114" s="54"/>
+      <c r="F114" s="32"/>
     </row>
     <row r="115" spans="2:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="61"/>
-      <c r="C115" s="62" t="str">
+      <c r="B115" s="45"/>
+      <c r="C115" s="37" t="str">
         <f>B17</f>
         <v>BUDGET TOTAL</v>
       </c>
-      <c r="D115" s="62">
+      <c r="D115" s="37">
         <f>IF(AND(_xlfn.ISFORMULA(E17),E17=SUM(E10:E16)),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E115" s="63">
+      <c r="E115" s="38">
         <v>1</v>
       </c>
-      <c r="F115" s="54"/>
+      <c r="F115" s="32"/>
     </row>
     <row r="116" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B116" s="64" t="s">
-        <v>115</v>
-      </c>
-      <c r="C116" s="62" t="str">
+      <c r="B116" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116" s="37" t="str">
         <f>F22</f>
         <v>Moyenne</v>
       </c>
-      <c r="D116" s="62">
+      <c r="D116" s="37">
         <f>IF(AND(_xlfn.ISFORMULA(F23),F23=AVERAGE(C23:E23)),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E116" s="63">
+      <c r="E116" s="38">
         <v>1</v>
       </c>
-      <c r="F116" s="54"/>
+      <c r="F116" s="32"/>
     </row>
     <row r="117" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B117" s="65" t="s">
-        <v>116</v>
-      </c>
-      <c r="C117" s="62" t="str">
+      <c r="B117" s="56" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117" s="37" t="str">
         <f>E32</f>
         <v>Économie</v>
       </c>
-      <c r="D117" s="62">
+      <c r="D117" s="37">
         <f>IF(AND(_xlfn.ISFORMULA(E33),E33=C33*D33/100),1,0)</f>
         <v>0</v>
       </c>
-      <c r="E117" s="63">
+      <c r="E117" s="38">
         <v>1</v>
       </c>
-      <c r="F117" s="54"/>
+      <c r="F117" s="32"/>
     </row>
     <row r="118" spans="2:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="66"/>
-      <c r="C118" s="62" t="str">
+      <c r="B118" s="57"/>
+      <c r="C118" s="37" t="str">
         <f>F32</f>
         <v>Prix final</v>
       </c>
-      <c r="D118" s="62">
+      <c r="D118" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F33),F33=C33-E33),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E118" s="63">
+      <c r="E118" s="38">
         <v>1</v>
       </c>
-      <c r="F118" s="54"/>
+      <c r="F118" s="32"/>
     </row>
     <row r="119" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B119" s="66"/>
-      <c r="C119" s="62" t="str">
+      <c r="B119" s="57"/>
+      <c r="C119" s="37" t="str">
         <f>B37</f>
         <v xml:space="preserve">TOTAL </v>
       </c>
-      <c r="D119" s="62">
+      <c r="D119" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F37),F37=SUM(F33:F36)),0.5,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E119" s="63">
+      <c r="E119" s="38">
         <v>0.5</v>
       </c>
-      <c r="F119" s="54"/>
+      <c r="F119" s="32"/>
     </row>
     <row r="120" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="67"/>
-      <c r="C120" s="62" t="str">
+      <c r="B120" s="58"/>
+      <c r="C120" s="37" t="str">
         <f>B37</f>
         <v xml:space="preserve">TOTAL </v>
       </c>
-      <c r="D120" s="62">
+      <c r="D120" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(E37),E37=SUM(E33:E36)),0.5,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E120" s="63">
+      <c r="E120" s="38">
         <v>0.5</v>
       </c>
-      <c r="F120" s="54"/>
+      <c r="F120" s="32"/>
     </row>
     <row r="121" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B121" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="C121" s="62" t="str">
+      <c r="B121" s="56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C121" s="37" t="str">
         <f>E43</f>
         <v>Vente MAX</v>
       </c>
-      <c r="D121" s="62">
+      <c r="D121" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F43),F43=MAX(C43:C49)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E121" s="63">
+      <c r="E121" s="38">
         <v>1</v>
       </c>
-      <c r="F121" s="54"/>
+      <c r="F121" s="32"/>
     </row>
     <row r="122" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="66"/>
-      <c r="C122" s="62" t="str">
+      <c r="B122" s="57"/>
+      <c r="C122" s="37" t="str">
         <f>E44</f>
         <v>Vente MIN</v>
       </c>
-      <c r="D122" s="62">
+      <c r="D122" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F44),F44=MIN(C43:C49)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E122" s="63">
+      <c r="E122" s="38">
         <v>1</v>
       </c>
-      <c r="F122" s="54"/>
+      <c r="F122" s="32"/>
     </row>
     <row r="123" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="66"/>
-      <c r="C123" s="62" t="str">
+      <c r="B123" s="57"/>
+      <c r="C123" s="37" t="str">
         <f>E45</f>
         <v>Vente moyenne</v>
       </c>
-      <c r="D123" s="62">
+      <c r="D123" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F45),F45=AVERAGE(C43:C49)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E123" s="63">
+      <c r="E123" s="38">
         <v>1</v>
       </c>
-      <c r="F123" s="54"/>
+      <c r="F123" s="32"/>
     </row>
     <row r="124" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B124" s="67"/>
-      <c r="C124" s="62" t="str">
+      <c r="B124" s="58"/>
+      <c r="C124" s="37" t="str">
         <f>E46</f>
         <v>Total semaine</v>
       </c>
-      <c r="D124" s="62">
+      <c r="D124" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F46),F46=SUM(C43:C49)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E124" s="63">
+      <c r="E124" s="38">
         <v>1</v>
       </c>
-      <c r="F124" s="54"/>
+      <c r="F124" s="32"/>
     </row>
     <row r="125" spans="2:6" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B125" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="C125" s="62" t="str">
+      <c r="B125" s="39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C125" s="37" t="str">
         <f>F55</f>
         <v>Points</v>
       </c>
-      <c r="D125" s="62">
+      <c r="D125" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F56),F56=C56*3+D56),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E125" s="63">
+      <c r="E125" s="38">
         <v>1</v>
       </c>
-      <c r="F125" s="54"/>
+      <c r="F125" s="32"/>
     </row>
     <row r="126" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B126" s="61" t="s">
-        <v>121</v>
-      </c>
-      <c r="C126" s="62" t="str">
+      <c r="B126" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="C126" s="37" t="str">
         <f>E67</f>
         <v>Total buts</v>
       </c>
-      <c r="D126" s="62">
+      <c r="D126" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F67),F67=SUM(C67:C73)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E126" s="63">
+      <c r="E126" s="38">
         <v>1</v>
       </c>
-      <c r="F126" s="54"/>
+      <c r="F126" s="32"/>
     </row>
     <row r="127" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="61"/>
-      <c r="C127" s="62" t="str">
+      <c r="B127" s="45"/>
+      <c r="C127" s="37" t="str">
         <f>E68</f>
         <v>Moyenne buts/match</v>
       </c>
-      <c r="D127" s="62">
+      <c r="D127" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F68),F68=AVERAGE(C67:C73)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E127" s="63">
+      <c r="E127" s="38">
         <v>1</v>
       </c>
-      <c r="F127" s="54"/>
+      <c r="F127" s="32"/>
     </row>
     <row r="128" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B128" s="61"/>
-      <c r="C128" s="62" t="str">
+      <c r="B128" s="45"/>
+      <c r="C128" s="37" t="str">
         <f>E69</f>
-        <v>Meilleure perf.</v>
-      </c>
-      <c r="D128" s="62">
+        <v>Meilleure performance</v>
+      </c>
+      <c r="D128" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F69),F69=MAX(C67:C73)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E128" s="63">
+      <c r="E128" s="38">
         <v>1</v>
       </c>
-      <c r="F128" s="54"/>
+      <c r="F128" s="32"/>
     </row>
     <row r="129" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B129" s="61"/>
-      <c r="C129" s="62" t="str">
+      <c r="B129" s="45"/>
+      <c r="C129" s="37" t="str">
         <f>E70</f>
-        <v>Plus mauvaise perf.</v>
-      </c>
-      <c r="D129" s="62">
+        <v>Plus mauvaise performance</v>
+      </c>
+      <c r="D129" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F70),F70=MIN(C67:C73)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E129" s="63">
+      <c r="E129" s="38">
         <v>1</v>
       </c>
-      <c r="F129" s="54"/>
+      <c r="F129" s="32"/>
     </row>
     <row r="130" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B130" s="61"/>
-      <c r="C130" s="62" t="str">
+      <c r="B130" s="45"/>
+      <c r="C130" s="37" t="str">
         <f>E71</f>
         <v>Nombre de matchs</v>
       </c>
-      <c r="D130" s="62">
+      <c r="D130" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(F71),F71=COUNT(C67:C73)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E130" s="63">
+      <c r="E130" s="38">
         <v>1</v>
       </c>
-      <c r="F130" s="54"/>
+      <c r="F130" s="32"/>
     </row>
     <row r="131" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B131" s="65" t="s">
-        <v>122</v>
-      </c>
-      <c r="C131" s="69" t="str">
+      <c r="B131" s="56" t="s">
+        <v>119</v>
+      </c>
+      <c r="C131" s="40" t="str">
         <f>E78</f>
         <v>Vitesse (km/h)</v>
       </c>
-      <c r="D131" s="62">
-        <f>IFERROR(IF(AND(_xlfn.ISFORMULA(E79),E79=C79/D79*100),1,0),0)</f>
+      <c r="D131" s="37">
+        <f>IFERROR(IF(AND(_xlfn.ISFORMULA(E79),E79=C79/D79*60),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E131" s="63">
+      <c r="E131" s="38">
         <v>1</v>
       </c>
-      <c r="F131" s="54"/>
+      <c r="F131" s="32"/>
     </row>
     <row r="132" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="67"/>
-      <c r="C132" s="69" t="str">
+      <c r="B132" s="58"/>
+      <c r="C132" s="40" t="str">
         <f>B84</f>
         <v>TOTAL</v>
       </c>
-      <c r="D132" s="62">
+      <c r="D132" s="37">
         <f>IFERROR(IF(AND(_xlfn.ISFORMULA(E84),E84=SUM(E79:E83)),1,0),0)</f>
         <v>0</v>
       </c>
-      <c r="E132" s="63">
+      <c r="E132" s="38">
         <v>1</v>
       </c>
-      <c r="F132" s="54"/>
+      <c r="F132" s="32"/>
     </row>
     <row r="133" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B133" s="61" t="s">
+      <c r="B133" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C133" s="70" t="s">
         <v>123</v>
       </c>
-      <c r="C133" s="70" t="s">
-        <v>126</v>
-      </c>
-      <c r="D133" s="62">
+      <c r="D133" s="37">
         <v>0</v>
       </c>
-      <c r="E133" s="63">
+      <c r="E133" s="38">
         <v>1</v>
       </c>
-      <c r="F133" s="54"/>
+      <c r="F133" s="32"/>
     </row>
     <row r="134" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="61"/>
+      <c r="B134" s="45"/>
       <c r="C134" s="70"/>
-      <c r="D134" s="62">
+      <c r="D134" s="37">
         <v>0</v>
       </c>
-      <c r="E134" s="63">
+      <c r="E134" s="38">
         <v>1</v>
       </c>
-      <c r="F134" s="54"/>
+      <c r="F134" s="32"/>
     </row>
     <row r="135" spans="2:6" ht="35.4" x14ac:dyDescent="0.3">
-      <c r="B135" s="54"/>
-      <c r="C135" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="D135" s="72">
+      <c r="B135" s="32"/>
+      <c r="C135" s="41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D135" s="42">
         <f>SUM(D114:D134)</f>
         <v>0</v>
       </c>
-      <c r="E135" s="73" t="str">
+      <c r="E135" s="43" t="str">
         <f>_xlfn.CONCAT("/",SUM(E114:E134))</f>
         <v>/20</v>
       </c>
-      <c r="F135" s="54"/>
+      <c r="F135" s="32"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ej1/5CjcmzYx7d6uvrJXLM/a2CJbglOURqIjwc1V0tPDpDcQYDcLbSrne+LjTT+2uf3BlVU+LtyDDlrDXeC5+w==" saltValue="BlquCHHTfBkajNGoDr8hvQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <mergeCells count="29">
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B88:D91"/>
-    <mergeCell ref="E88:G91"/>
-    <mergeCell ref="B117:B120"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B76:E76"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="pjIUw86zq2L6x4wd4A3lTov9+lcmtc+cxovM3k0mRMeke8KpYEUAwgCjV96q/d4KDs9eG2i1F3mbSDri0S6C4Q==" saltValue="yL9QTthOYbzUk1uVCZtthw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="30">
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="B121:B124"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="B131:B132"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="F30:K30"/>
     <mergeCell ref="L30:Q30"/>
@@ -3280,12 +3287,18 @@
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="F20:K20"/>
     <mergeCell ref="B37:D37"/>
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="B121:B124"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="F52:K52"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="B88:D91"/>
+    <mergeCell ref="E88:G91"/>
+    <mergeCell ref="B117:B120"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="D114:D134">
@@ -3307,6 +3320,9 @@
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="H4:H5" unlockedFormula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/TP2026/Exercices_TP8.xlsx
+++ b/TP2026/Exercices_TP8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tahto\OneDrive\Documents\GitHub\u3\TP2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98E11E3D-4308-4CEE-B733-609565694312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A779350-15B8-41F0-8C0D-C7C1F621FF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{77D2F8F8-3EAB-4FD5-8A99-8A7B70AECDED}"/>
   </bookViews>
@@ -1030,52 +1030,25 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -1089,6 +1062,34 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1104,49 +1105,48 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1835,11 +1835,11 @@
       <c r="B4" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
       <c r="G4" s="4" t="s">
         <v>91</v>
       </c>
@@ -1852,11 +1852,11 @@
       <c r="B5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="66" t="s">
+      <c r="C5" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
       <c r="G5" s="4" t="s">
         <v>93</v>
       </c>
@@ -1866,20 +1866,20 @@
       </c>
     </row>
     <row r="7" spans="2:31" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
-      <c r="F7" s="64" t="s">
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
+      <c r="E7" s="52"/>
+      <c r="F7" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="53"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="53"/>
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.3">
       <c r="AE8" s="9" t="s">
@@ -2023,30 +2023,30 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.3">
-      <c r="B17" s="67" t="s">
+      <c r="B17" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="67"/>
-      <c r="D17" s="67"/>
+      <c r="C17" s="56"/>
+      <c r="D17" s="56"/>
       <c r="E17" s="17" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="20" spans="2:17" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="52" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="63"/>
-      <c r="D20" s="63"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="64" t="s">
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="64"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
+      <c r="G20" s="53"/>
+      <c r="H20" s="53"/>
+      <c r="I20" s="53"/>
+      <c r="J20" s="53"/>
+      <c r="K20" s="53"/>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B22" s="10" t="s">
@@ -2151,28 +2151,28 @@
       </c>
     </row>
     <row r="30" spans="2:17" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
-      <c r="F30" s="64" t="s">
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="G30" s="64"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="64"/>
-      <c r="J30" s="64"/>
-      <c r="K30" s="64"/>
-      <c r="L30" s="65" t="s">
+      <c r="G30" s="53"/>
+      <c r="H30" s="53"/>
+      <c r="I30" s="53"/>
+      <c r="J30" s="53"/>
+      <c r="K30" s="53"/>
+      <c r="L30" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="M30" s="65"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="65"/>
-      <c r="P30" s="65"/>
-      <c r="Q30" s="65"/>
+      <c r="M30" s="54"/>
+      <c r="N30" s="54"/>
+      <c r="O30" s="54"/>
+      <c r="P30" s="54"/>
+      <c r="Q30" s="54"/>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.3">
       <c r="B32" s="10" t="s">
@@ -2260,11 +2260,11 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B37" s="68" t="s">
+      <c r="B37" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
       <c r="E37" s="18" t="s">
         <v>128</v>
       </c>
@@ -2375,20 +2375,20 @@
       </c>
     </row>
     <row r="52" spans="2:11" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="63" t="s">
+      <c r="B52" s="52" t="s">
         <v>107</v>
       </c>
-      <c r="C52" s="63"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
-      <c r="F52" s="64" t="s">
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="G52" s="64"/>
-      <c r="H52" s="64"/>
-      <c r="I52" s="64"/>
-      <c r="J52" s="64"/>
-      <c r="K52" s="64"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="53"/>
+      <c r="K52" s="53"/>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53" s="62" t="s">
@@ -2501,12 +2501,12 @@
       </c>
     </row>
     <row r="63" spans="2:11" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="63" t="s">
+      <c r="B63" s="52" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="63"/>
-      <c r="D63" s="63"/>
-      <c r="E63" s="63"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64" s="62" t="s">
@@ -2617,12 +2617,12 @@
       </c>
     </row>
     <row r="75" spans="2:6" s="8" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B75" s="63" t="s">
+      <c r="B75" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="C75" s="63"/>
-      <c r="D75" s="63"/>
-      <c r="E75" s="63"/>
+      <c r="C75" s="52"/>
+      <c r="D75" s="52"/>
+      <c r="E75" s="52"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B76" s="62" t="s">
@@ -2727,49 +2727,49 @@
       </c>
     </row>
     <row r="86" spans="2:7" s="29" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="44" t="s">
+      <c r="B86" s="63" t="s">
         <v>106</v>
       </c>
-      <c r="C86" s="44"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="44"/>
+      <c r="C86" s="63"/>
+      <c r="D86" s="63"/>
+      <c r="E86" s="63"/>
     </row>
     <row r="87" spans="2:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="88" spans="2:7" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B88" s="46" t="s">
+      <c r="B88" s="64" t="s">
         <v>85</v>
       </c>
-      <c r="C88" s="46"/>
-      <c r="D88" s="46"/>
-      <c r="E88" s="47" t="s">
+      <c r="C88" s="64"/>
+      <c r="D88" s="64"/>
+      <c r="E88" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="F88" s="48"/>
-      <c r="G88" s="49"/>
+      <c r="F88" s="66"/>
+      <c r="G88" s="67"/>
     </row>
     <row r="89" spans="2:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="46"/>
-      <c r="C89" s="46"/>
-      <c r="D89" s="46"/>
-      <c r="E89" s="50"/>
-      <c r="F89" s="51"/>
-      <c r="G89" s="52"/>
+      <c r="B89" s="64"/>
+      <c r="C89" s="64"/>
+      <c r="D89" s="64"/>
+      <c r="E89" s="68"/>
+      <c r="F89" s="69"/>
+      <c r="G89" s="70"/>
     </row>
     <row r="90" spans="2:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B90" s="46"/>
-      <c r="C90" s="46"/>
-      <c r="D90" s="46"/>
-      <c r="E90" s="50"/>
-      <c r="F90" s="51"/>
-      <c r="G90" s="52"/>
+      <c r="B90" s="64"/>
+      <c r="C90" s="64"/>
+      <c r="D90" s="64"/>
+      <c r="E90" s="68"/>
+      <c r="F90" s="69"/>
+      <c r="G90" s="70"/>
     </row>
     <row r="91" spans="2:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B91" s="46"/>
-      <c r="C91" s="46"/>
-      <c r="D91" s="46"/>
-      <c r="E91" s="53"/>
-      <c r="F91" s="54"/>
-      <c r="G91" s="55"/>
+      <c r="B91" s="64"/>
+      <c r="C91" s="64"/>
+      <c r="D91" s="64"/>
+      <c r="E91" s="71"/>
+      <c r="F91" s="72"/>
+      <c r="G91" s="73"/>
     </row>
     <row r="94" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B94" s="30" t="s">
@@ -2906,11 +2906,11 @@
     </row>
     <row r="112" spans="2:7" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B112" s="32"/>
-      <c r="C112" s="71" t="s">
+      <c r="C112" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="D112" s="72"/>
-      <c r="E112" s="73"/>
+      <c r="D112" s="47"/>
+      <c r="E112" s="48"/>
       <c r="F112" s="32"/>
     </row>
     <row r="113" spans="2:6" ht="18" x14ac:dyDescent="0.3">
@@ -2927,7 +2927,7 @@
       <c r="F113" s="32"/>
     </row>
     <row r="114" spans="2:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B114" s="45" t="s">
+      <c r="B114" s="44" t="s">
         <v>111</v>
       </c>
       <c r="C114" s="37" t="str">
@@ -2944,7 +2944,7 @@
       <c r="F114" s="32"/>
     </row>
     <row r="115" spans="2:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="45"/>
+      <c r="B115" s="44"/>
       <c r="C115" s="37" t="str">
         <f>B17</f>
         <v>BUDGET TOTAL</v>
@@ -2976,7 +2976,7 @@
       <c r="F116" s="32"/>
     </row>
     <row r="117" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B117" s="56" t="s">
+      <c r="B117" s="49" t="s">
         <v>113</v>
       </c>
       <c r="C117" s="37" t="str">
@@ -2993,7 +2993,7 @@
       <c r="F117" s="32"/>
     </row>
     <row r="118" spans="2:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="57"/>
+      <c r="B118" s="50"/>
       <c r="C118" s="37" t="str">
         <f>F32</f>
         <v>Prix final</v>
@@ -3008,7 +3008,7 @@
       <c r="F118" s="32"/>
     </row>
     <row r="119" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B119" s="57"/>
+      <c r="B119" s="50"/>
       <c r="C119" s="37" t="str">
         <f>B37</f>
         <v xml:space="preserve">TOTAL </v>
@@ -3023,7 +3023,7 @@
       <c r="F119" s="32"/>
     </row>
     <row r="120" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="58"/>
+      <c r="B120" s="51"/>
       <c r="C120" s="37" t="str">
         <f>B37</f>
         <v xml:space="preserve">TOTAL </v>
@@ -3038,7 +3038,7 @@
       <c r="F120" s="32"/>
     </row>
     <row r="121" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B121" s="56" t="s">
+      <c r="B121" s="49" t="s">
         <v>116</v>
       </c>
       <c r="C121" s="37" t="str">
@@ -3055,7 +3055,7 @@
       <c r="F121" s="32"/>
     </row>
     <row r="122" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="57"/>
+      <c r="B122" s="50"/>
       <c r="C122" s="37" t="str">
         <f>E44</f>
         <v>Vente MIN</v>
@@ -3070,7 +3070,7 @@
       <c r="F122" s="32"/>
     </row>
     <row r="123" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="57"/>
+      <c r="B123" s="50"/>
       <c r="C123" s="37" t="str">
         <f>E45</f>
         <v>Vente moyenne</v>
@@ -3085,7 +3085,7 @@
       <c r="F123" s="32"/>
     </row>
     <row r="124" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B124" s="58"/>
+      <c r="B124" s="51"/>
       <c r="C124" s="37" t="str">
         <f>E46</f>
         <v>Total semaine</v>
@@ -3117,7 +3117,7 @@
       <c r="F125" s="32"/>
     </row>
     <row r="126" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B126" s="45" t="s">
+      <c r="B126" s="44" t="s">
         <v>118</v>
       </c>
       <c r="C126" s="37" t="str">
@@ -3134,7 +3134,7 @@
       <c r="F126" s="32"/>
     </row>
     <row r="127" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="45"/>
+      <c r="B127" s="44"/>
       <c r="C127" s="37" t="str">
         <f>E68</f>
         <v>Moyenne buts/match</v>
@@ -3149,7 +3149,7 @@
       <c r="F127" s="32"/>
     </row>
     <row r="128" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B128" s="45"/>
+      <c r="B128" s="44"/>
       <c r="C128" s="37" t="str">
         <f>E69</f>
         <v>Meilleure performance</v>
@@ -3164,7 +3164,7 @@
       <c r="F128" s="32"/>
     </row>
     <row r="129" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B129" s="45"/>
+      <c r="B129" s="44"/>
       <c r="C129" s="37" t="str">
         <f>E70</f>
         <v>Plus mauvaise performance</v>
@@ -3179,7 +3179,7 @@
       <c r="F129" s="32"/>
     </row>
     <row r="130" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B130" s="45"/>
+      <c r="B130" s="44"/>
       <c r="C130" s="37" t="str">
         <f>E71</f>
         <v>Nombre de matchs</v>
@@ -3194,7 +3194,7 @@
       <c r="F130" s="32"/>
     </row>
     <row r="131" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B131" s="56" t="s">
+      <c r="B131" s="49" t="s">
         <v>119</v>
       </c>
       <c r="C131" s="40" t="str">
@@ -3211,7 +3211,7 @@
       <c r="F131" s="32"/>
     </row>
     <row r="132" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="58"/>
+      <c r="B132" s="51"/>
       <c r="C132" s="40" t="str">
         <f>B84</f>
         <v>TOTAL</v>
@@ -3226,10 +3226,10 @@
       <c r="F132" s="32"/>
     </row>
     <row r="133" spans="2:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="B133" s="45" t="s">
+      <c r="B133" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="C133" s="70" t="s">
+      <c r="C133" s="45" t="s">
         <v>123</v>
       </c>
       <c r="D133" s="37">
@@ -3241,8 +3241,8 @@
       <c r="F133" s="32"/>
     </row>
     <row r="134" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="45"/>
-      <c r="C134" s="70"/>
+      <c r="B134" s="44"/>
+      <c r="C134" s="45"/>
       <c r="D134" s="37">
         <v>0</v>
       </c>
@@ -3269,12 +3269,17 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="pjIUw86zq2L6x4wd4A3lTov9+lcmtc+cxovM3k0mRMeke8KpYEUAwgCjV96q/d4KDs9eG2i1F3mbSDri0S6C4Q==" saltValue="yL9QTthOYbzUk1uVCZtthw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="30">
-    <mergeCell ref="B133:B134"/>
-    <mergeCell ref="C133:C134"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="B121:B124"/>
-    <mergeCell ref="B126:B130"/>
-    <mergeCell ref="B131:B132"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B114:B115"/>
+    <mergeCell ref="B88:D91"/>
+    <mergeCell ref="E88:G91"/>
+    <mergeCell ref="B117:B120"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B63:E63"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B76:E76"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="F30:K30"/>
     <mergeCell ref="L30:Q30"/>
@@ -3288,17 +3293,12 @@
     <mergeCell ref="F20:K20"/>
     <mergeCell ref="B37:D37"/>
     <mergeCell ref="F52:K52"/>
-    <mergeCell ref="B84:D84"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B63:E63"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="B114:B115"/>
-    <mergeCell ref="B88:D91"/>
-    <mergeCell ref="E88:G91"/>
-    <mergeCell ref="B117:B120"/>
+    <mergeCell ref="B133:B134"/>
+    <mergeCell ref="C133:C134"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="B121:B124"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="B131:B132"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <conditionalFormatting sqref="D114:D134">
